--- a/Test_Data/登陆数据.xlsx
+++ b/Test_Data/登陆数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13460"/>
+    <workbookView windowWidth="29100" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="MD登陆数据" sheetId="4" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="126">
   <si>
     <t>url</t>
   </si>
@@ -178,9 +178,6 @@
   </si>
   <si>
     <t>00003195</t>
-  </si>
-  <si>
-    <t>sc+seeltestew01@seel.com</t>
   </si>
   <si>
     <t>ordernumber</t>
@@ -1055,7 +1052,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1075,9 +1072,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1379,13 +1373,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1402,7 +1396,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4923790" y="1696720"/>
+          <a:off x="4923790" y="416560"/>
           <a:ext cx="254000" cy="254000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1420,13 +1414,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1443,7 +1437,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2835910" y="1696720"/>
+          <a:off x="2835910" y="416560"/>
           <a:ext cx="254000" cy="254000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1461,13 +1455,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>40640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1484,7 +1478,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4923790" y="1910080"/>
+          <a:off x="4923790" y="416560"/>
           <a:ext cx="254000" cy="254000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1751,7 +1745,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="42.9423076923077" customWidth="1"/>
@@ -1762,369 +1756,366 @@
     <col min="6" max="6" width="26.5961538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="7" customFormat="1" spans="1:6">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="8" customFormat="1" ht="16" customHeight="1" spans="1:6">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="7" customFormat="1" ht="16" customHeight="1" spans="1:6">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:6">
-      <c r="A3" s="9" t="s">
+    <row r="3" s="7" customFormat="1" spans="1:6">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:6">
-      <c r="A4" s="8" t="s">
+    <row r="4" s="7" customFormat="1" spans="1:6">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:6">
-      <c r="A5" s="9" t="s">
+    <row r="5" s="7" customFormat="1" spans="1:6">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" spans="1:6">
-      <c r="A6" s="9" t="s">
+    <row r="6" s="7" customFormat="1" spans="1:6">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="1" spans="1:6">
-      <c r="A7" s="9" t="s">
+    <row r="7" s="7" customFormat="1" spans="1:6">
+      <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="1" spans="1:6">
-      <c r="A8" s="9" t="s">
+    <row r="8" s="7" customFormat="1" spans="1:6">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" s="8" customFormat="1" spans="1:6">
-      <c r="A9" s="9" t="s">
+    <row r="9" s="7" customFormat="1" spans="1:6">
+      <c r="A9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" s="8" customFormat="1" spans="1:6">
-      <c r="A10" s="9" t="s">
+    <row r="10" s="7" customFormat="1" spans="1:6">
+      <c r="A10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" s="8" customFormat="1" spans="1:6">
-      <c r="A11" s="9" t="s">
+    <row r="11" s="7" customFormat="1" spans="1:6">
+      <c r="A11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:6">
-      <c r="A12" s="9" t="s">
+    <row r="12" s="7" customFormat="1" spans="1:6">
+      <c r="A12" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="8" customFormat="1" ht="17" spans="1:6">
-      <c r="A13" s="9" t="s">
+    <row r="13" s="7" customFormat="1" ht="17" spans="1:6">
+      <c r="A13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:6">
-      <c r="A14" s="9" t="s">
+    <row r="14" s="7" customFormat="1" spans="1:6">
+      <c r="A14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:6">
-      <c r="A15" s="9" t="s">
+    <row r="15" s="7" customFormat="1" spans="1:6">
+      <c r="A15" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" s="8" customFormat="1" spans="1:6">
-      <c r="A16" s="9" t="s">
+    <row r="16" s="7" customFormat="1" spans="1:6">
+      <c r="A16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" s="8" customFormat="1" spans="1:6">
-      <c r="A17" s="9" t="s">
+    <row r="17" s="7" customFormat="1" spans="1:6">
+      <c r="A17" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" s="8" customFormat="1" spans="1:6">
-      <c r="A18" s="9" t="s">
+    <row r="18" s="7" customFormat="1" spans="1:6">
+      <c r="A18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" s="8" customFormat="1"/>
-    <row r="20" s="8" customFormat="1"/>
-    <row r="21" s="8" customFormat="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A8" r:id="rId2" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
@@ -2192,7 +2183,7 @@
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2208,7 +2199,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="42.9423076923077" customWidth="1"/>
@@ -2239,164 +2230,344 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="1" spans="1:6">
-      <c r="A2" t="s">
+    <row r="2" s="7" customFormat="1" ht="16" customHeight="1" spans="1:6">
+      <c r="A2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:6">
-      <c r="A3" t="s">
+    <row r="3" s="7" customFormat="1" spans="1:6">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:6">
-      <c r="A4" t="s">
+    <row r="4" s="7" customFormat="1" spans="1:6">
+      <c r="A4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" t="s">
+    <row r="5" s="7" customFormat="1" spans="1:6">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
-      <c r="A6" s="2" t="s">
+    <row r="6" s="7" customFormat="1" spans="1:6">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:6">
-      <c r="A7" s="2" t="s">
+    <row r="7" s="7" customFormat="1" spans="1:6">
+      <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:6">
-      <c r="A8" s="2" t="s">
+    <row r="8" s="7" customFormat="1" spans="1:6">
+      <c r="A8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
-      <c r="A9" s="2" t="s">
+    <row r="9" s="7" customFormat="1" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="7" customFormat="1" spans="1:6">
+      <c r="A10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" s="7" customFormat="1" spans="1:6">
+      <c r="A11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" s="7" customFormat="1" spans="1:6">
+      <c r="A12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9">
-        <v>123123</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="C12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
-        <v>25</v>
+      <c r="F12" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" s="7" customFormat="1" ht="17" spans="1:6">
+      <c r="A13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="7" customFormat="1" spans="1:6">
+      <c r="A14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="7" customFormat="1" spans="1:6">
+      <c r="A15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" s="7" customFormat="1" spans="1:6">
+      <c r="A16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" s="7" customFormat="1" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" s="7" customFormat="1" spans="1:6">
+      <c r="A18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2577,29 @@
     <hyperlink ref="C5" r:id="rId3" display="kai.li@seel.com" tooltip="mailto:kai.li@seel.com"/>
     <hyperlink ref="A7" r:id="rId1" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
     <hyperlink ref="A6" r:id="rId1" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
-    <hyperlink ref="A9" r:id="rId4" display="https://dashboard.seel.com/"/>
+    <hyperlink ref="A11" r:id="rId4" display="https://dashboard.seel.com/" tooltip="https://dashboard.seel.com/"/>
+    <hyperlink ref="C11" r:id="rId5" display="yuchen.song+1200@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A12" r:id="rId4" display="https://dashboard.seel.com/"/>
+    <hyperlink ref="C12" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="C13" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A13" r:id="rId4" display="https://dashboard.seel.com/"/>
+    <hyperlink ref="A14" r:id="rId4" display="https://dashboard.seel.com/"/>
+    <hyperlink ref="C14" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A15" r:id="rId4" display="https://dashboard.seel.com/" tooltip="https://dashboard.seel.com/"/>
+    <hyperlink ref="C15" r:id="rId5" display="yuchen.song+1200@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="C16" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A16" r:id="rId4" display="https://dashboard.seel.com/" tooltip="https://dashboard.seel.com/"/>
+    <hyperlink ref="C17" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A17" r:id="rId4" display="https://dashboard.seel.com/" tooltip="https://dashboard.seel.com/"/>
+    <hyperlink ref="C18" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A18" r:id="rId4" display="https://dashboard.seel.com/" tooltip="https://dashboard.seel.com/"/>
+    <hyperlink ref="C9" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="C10" r:id="rId5" display="yuchen.song@seel.com" tooltip="mailto:yuchen.song@seel.com"/>
+    <hyperlink ref="A9" r:id="rId1" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
+    <hyperlink ref="A10" r:id="rId1" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
+    <hyperlink ref="A2" r:id="rId6" display="https://dashboard-dev.seel.com/" tooltip="https://dashboard-dev.seel.com/"/>
+    <hyperlink ref="A3" r:id="rId6" display="https://dashboard-dev.seel.com/" tooltip="https://dashboard-dev.seel.com/"/>
+    <hyperlink ref="A5" r:id="rId6" display="https://dashboard-dev.seel.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2437,7 +2630,7 @@
         <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:4">
@@ -2447,10 +2640,10 @@
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2461,10 +2654,10 @@
       <c r="B3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2473,12 +2666,12 @@
         <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2487,349 +2680,349 @@
         <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
       <c r="A7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
       <c r="A10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" t="s">
         <v>59</v>
       </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
       <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
         <v>59</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:4">
       <c r="A15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" spans="1:4">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" spans="1:4">
       <c r="A18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" spans="1:4">
       <c r="A19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:4">
       <c r="A20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" spans="1:4">
       <c r="A21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:4">
       <c r="A22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" spans="1:4">
       <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:4">
       <c r="A24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:4">
       <c r="A25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" spans="1:4">
       <c r="A26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:4">
       <c r="A27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:4">
       <c r="A28" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:4">
       <c r="A29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:4">
@@ -2837,13 +3030,13 @@
         <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:4">
@@ -2851,13 +3044,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" spans="1:4">
@@ -2865,13 +3058,13 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:4">
@@ -2879,349 +3072,349 @@
         <v>19</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:4">
       <c r="A34" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B34" t="s">
-        <v>54</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="D34" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" spans="1:4">
       <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" spans="1:4">
       <c r="A36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
       <c r="D36" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" spans="1:4">
       <c r="A37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" spans="1:4">
       <c r="A38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" spans="1:4">
       <c r="A39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B39" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" spans="1:4">
       <c r="A40" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" spans="1:4">
       <c r="A41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" spans="1:4">
       <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" t="s">
         <v>84</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:4">
       <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" t="s">
         <v>84</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" spans="1:4">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:4">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" spans="1:4">
       <c r="A46" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="D46" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" spans="1:4">
       <c r="A47" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B47" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" spans="1:4">
       <c r="A48" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" spans="1:4">
       <c r="A49" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="17.6" spans="1:4">
       <c r="A50" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D50" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" spans="1:4">
       <c r="A51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" spans="1:4">
       <c r="A52" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D52" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" spans="1:4">
       <c r="A53" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" spans="1:4">
       <c r="A54" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="D54" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" spans="1:4">
       <c r="A55" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" spans="1:4">
       <c r="A56" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" s="1" customFormat="1" spans="1:4">
       <c r="A57" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" s="1" customFormat="1" spans="1:4">
@@ -3229,13 +3422,13 @@
         <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="59" s="1" customFormat="1" spans="1:4">
@@ -3243,13 +3436,13 @@
         <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" s="1" customFormat="1" spans="1:4">
@@ -3257,13 +3450,13 @@
         <v>23</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:4">
@@ -3271,125 +3464,125 @@
         <v>23</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:4">
       <c r="A62" t="s">
+        <v>99</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="s">
         <v>100</v>
       </c>
-      <c r="B62" t="s">
-        <v>54</v>
-      </c>
-      <c r="C62" t="s">
-        <v>101</v>
-      </c>
       <c r="D62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" s="1" customFormat="1" spans="1:4">
       <c r="A63" t="s">
+        <v>99</v>
+      </c>
+      <c r="B63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D63" t="s">
         <v>100</v>
-      </c>
-      <c r="B63" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D63" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="64" s="1" customFormat="1" spans="1:4">
       <c r="A64" t="s">
+        <v>99</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C64" t="s">
-        <v>101</v>
-      </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" s="1" customFormat="1" spans="1:4">
       <c r="A65" t="s">
+        <v>99</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D65" t="s">
         <v>100</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D65" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:4">
       <c r="A66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
         <v>103</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" t="s">
-        <v>104</v>
-      </c>
       <c r="D66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:4">
       <c r="A67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D67" t="s">
         <v>103</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:4">
       <c r="A68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C68" t="s">
         <v>103</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C68" t="s">
-        <v>104</v>
-      </c>
       <c r="D68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:4">
       <c r="A69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D69" t="s">
         <v>103</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D69" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3431,13 +3624,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s">
         <v>106</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>107</v>
-      </c>
-      <c r="C1" t="s">
-        <v>108</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -3445,212 +3638,212 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s">
         <v>109</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>110</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>111</v>
-      </c>
-      <c r="D2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" t="s">
         <v>109</v>
       </c>
-      <c r="B3" t="s">
-        <v>110</v>
-      </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" t="s">
         <v>109</v>
       </c>
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
         <v>115</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>116</v>
       </c>
-      <c r="C5" t="s">
-        <v>117</v>
-      </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
         <v>115</v>
       </c>
-      <c r="B6" t="s">
-        <v>116</v>
-      </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
         <v>115</v>
       </c>
-      <c r="B7" t="s">
-        <v>116</v>
-      </c>
       <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" t="s">
         <v>111</v>
-      </c>
-      <c r="D7" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B8" t="s">
         <v>119</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>120</v>
       </c>
-      <c r="C8" t="s">
-        <v>121</v>
-      </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" t="s">
         <v>119</v>
       </c>
-      <c r="B9" t="s">
-        <v>120</v>
-      </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
         <v>119</v>
       </c>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B11" t="s">
         <v>123</v>
       </c>
-      <c r="B11" t="s">
-        <v>124</v>
-      </c>
       <c r="C11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" t="s">
         <v>123</v>
       </c>
-      <c r="B12" t="s">
-        <v>124</v>
-      </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
         <v>123</v>
       </c>
-      <c r="B13" t="s">
-        <v>124</v>
-      </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
         <v>125</v>
       </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" t="s">
         <v>125</v>
       </c>
-      <c r="B15" t="s">
-        <v>126</v>
-      </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" t="s">
         <v>125</v>
       </c>
-      <c r="B16" t="s">
-        <v>126</v>
-      </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Test_Data/登陆数据.xlsx
+++ b/Test_Data/登陆数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13420"/>
+    <workbookView windowWidth="29100" windowHeight="13440"/>
   </bookViews>
   <sheets>
     <sheet name="MD登陆数据" sheetId="4" r:id="rId1"/>
@@ -2145,7 +2145,7 @@
     <hyperlink ref="A10" r:id="rId2" display="https://dashboard-test.seel.com/" tooltip="https://dashboard-test.seel.com/"/>
     <hyperlink ref="A2" r:id="rId7" display="https://dashboard-dev.seel.com/" tooltip="https://dashboard-dev.seel.com/"/>
     <hyperlink ref="A3" r:id="rId7" display="https://dashboard-dev.seel.com/" tooltip="https://dashboard-dev.seel.com/"/>
-    <hyperlink ref="A5" r:id="rId7" display="https://dashboard-dev.seel.com/"/>
+    <hyperlink ref="A5" r:id="rId7" display="https://dashboard-dev.seel.com/" tooltip="https://dashboard-dev.seel.com/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
